--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488103_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488103_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6131</v>
+        <v>3.5971</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6934</v>
+        <v>3.6725</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9197</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8803</v>
+        <v>0.3859</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1694</v>
+        <v>-2.381</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.289</v>
+        <v>2.7668</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8472</v>
+        <v>2.2952</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0838</v>
+        <v>0.0945</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7634</v>
+        <v>2.2007</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9668</v>
+        <v>-1.9094</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0856</v>
+        <v>-2.4755</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0524</v>
+        <v>0.5661</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5947</v>
+        <v>2.3787</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.1716</v>
+        <v>-1.1893</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5769</v>
+        <v>3.568</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0609</v>
+        <v>-0.0376</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7513</v>
+        <v>0.4894</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3096</v>
+        <v>-0.5269</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2666</v>
+        <v>0.8701</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2666</v>
+        <v>2.0772</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2332</v>
+        <v>1.4884</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3647</v>
+        <v>-0.2629</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1316</v>
+        <v>1.7512</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3859</v>
+        <v>0.8803</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.381</v>
+        <v>1.1694</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7668</v>
+        <v>-0.289</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2952</v>
+        <v>1.8472</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0945</v>
+        <v>1.0838</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2007</v>
+        <v>0.7634</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9094</v>
+        <v>-0.9668</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.4755</v>
+        <v>0.0856</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5661</v>
+        <v>-1.0524</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3787</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1893</v>
+        <v>-3.1716</v>
       </c>
       <c r="R3" t="n">
-        <v>3.568</v>
+        <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4015</v>
+        <v>0.9361</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8184</v>
+        <v>0.795</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5831</v>
+        <v>0.1412</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8701</v>
+        <v>0.2666</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0772</v>
+        <v>0.2666</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. TERRON FERNANDEZ</t>
+          <t>R. VIDALES MOLINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0882</v>
+        <v>1.3425</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2253</v>
+        <v>0.0625</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8629</v>
+        <v>1.28</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7034</v>
+        <v>-2.7198</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8848</v>
+        <v>-3.6535</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8186</v>
+        <v>0.9337</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7933</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5857</v>
+        <v>-2.5943</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.379</v>
+        <v>1.856</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9101</v>
+        <v>-1.9814</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4705</v>
+        <v>-1.0591</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5604</v>
+        <v>-0.9223</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1893</v>
+        <v>3.568</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1716</v>
+        <v>3.568</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6023</v>
+        <v>0.2277</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3973</v>
+        <v>0.5343</v>
       </c>
       <c r="U4" t="n">
-        <v>0.205</v>
+        <v>-0.3066</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6036</v>
+        <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. VIDALES MOLINA</t>
+          <t>D. TERRÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8954</v>
+        <v>0.6027</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3284</v>
+        <v>0.6027</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2238</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.7198</v>
+        <v>0.6027</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.6535</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9337</v>
+        <v>0.6027</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7383999999999999</v>
+        <v>0.6027</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.5943</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.856</v>
+        <v>0.6027</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9814</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0591</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9223</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.568</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.568</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2194</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1434</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3628</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. TERRÓN FERNÁNDEZ</t>
+          <t>D. TERRON FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6027</v>
+        <v>0.5799</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6027</v>
+        <v>-0.9742</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.554</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6027</v>
+        <v>-1.7034</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.8848</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6027</v>
+        <v>-0.8186</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6027</v>
+        <v>-0.7933</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.5857</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6027</v>
+        <v>-1.379</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.9101</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.4705</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.5604</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.1716</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.0939</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.1978</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.1039</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.245</v>
+        <v>0.3029</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1822</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9372</v>
+        <v>1.0776</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8929</v>
@@ -1000,13 +1000,13 @@
         <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5414</v>
+        <v>0.0065</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4661</v>
+        <v>-0.0586</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9765</v>
+        <v>-0.6604</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8482</v>
+        <v>-0.6444</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1283</v>
+        <v>-0.016</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9266</v>
@@ -1078,13 +1078,13 @@
         <v>0.3964</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4464</v>
+        <v>-0.1303</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2496</v>
+        <v>-0.0459</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1968</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>E. LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0337</v>
+        <v>-0.9323</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3043</v>
+        <v>-0.2886</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7294</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1397</v>
+        <v>-0.1366</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5433</v>
+        <v>-0.3834</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4036</v>
+        <v>0.2468</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4503</v>
+        <v>0.663</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3298</v>
+        <v>0.0202</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1205</v>
+        <v>0.6428</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.59</v>
+        <v>-0.7996</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8731</v>
+        <v>-0.4036</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2831</v>
+        <v>-0.3961</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3876</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1339</v>
+        <v>-0.0028</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1176</v>
+        <v>0.0395</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2515</v>
+        <v>-0.0422</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1476</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. LOPEZ GARCIA</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0903</v>
+        <v>-1.0971</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3905</v>
+        <v>-0.5081</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6998</v>
+        <v>-0.589</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1366</v>
+        <v>-0.1397</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3834</v>
+        <v>-0.5433</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2468</v>
+        <v>0.4036</v>
       </c>
       <c r="J10" t="n">
-        <v>0.663</v>
+        <v>0.4503</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0202</v>
+        <v>0.3298</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6428</v>
+        <v>0.1205</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7996</v>
+        <v>-0.59</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4036</v>
+        <v>-0.8731</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3961</v>
+        <v>0.2831</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1608</v>
+        <v>-0.1973</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0624</v>
+        <v>-0.0862</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0984</v>
+        <v>-0.1111</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.1476</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. CABRERA RUIZ</t>
+          <t>D. NARANJO FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4632</v>
+        <v>-1.2461</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8636</v>
+        <v>-2.3474</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4004</v>
+        <v>1.1013</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8428</v>
+        <v>-2.148</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5123</v>
+        <v>0.4252</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6695</v>
+        <v>-2.5732</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8563</v>
+        <v>-1.9768</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9769</v>
+        <v>-0.06</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1205</v>
+        <v>-1.9169</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0136</v>
+        <v>-0.1711</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5355</v>
+        <v>0.4852</v>
       </c>
       <c r="O11" t="n">
-        <v>0.549</v>
+        <v>-0.6563</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3964</v>
+        <v>2.3787</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5947</v>
+        <v>2.3787</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7761</v>
+        <v>-0.2698</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9839</v>
+        <v>-0.3706</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2078</v>
+        <v>0.1008</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. NARANJO FERNANDEZ</t>
+          <t>G. CABRERA RUIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8346</v>
+        <v>-1.9621</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8797</v>
+        <v>-2.4748</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0451</v>
+        <v>0.5127</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.148</v>
+        <v>-1.8428</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4252</v>
+        <v>-2.5123</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.5732</v>
+        <v>0.6695</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9768</v>
+        <v>-1.8563</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.06</v>
+        <v>-1.9769</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9169</v>
+        <v>0.1205</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1711</v>
+        <v>0.0136</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4852</v>
+        <v>-0.5355</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6563</v>
+        <v>0.549</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3787</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3787</v>
+        <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8582</v>
+        <v>0.2772</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9029</v>
+        <v>0.3727</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0447</v>
+        <v>-0.0955</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3833</v>
+        <v>-2.7356</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2689</v>
+        <v>-1.8177</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1144</v>
+        <v>-0.9179</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1973</v>
@@ -1468,13 +1468,13 @@
         <v>2.1805</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0122</v>
+        <v>0.6599</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7806</v>
+        <v>1.2317</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7684</v>
+        <v>-0.5718</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.2001</v>
+        <v>-4.1378</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.5964</v>
+        <v>-1.0849</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.6037</v>
+        <v>-3.0529</v>
       </c>
       <c r="G14" t="n">
         <v>-3.4325</v>
@@ -1546,13 +1546,13 @@
         <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0007</v>
+        <v>0.0615</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2772</v>
+        <v>0.2342</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2765</v>
+        <v>-0.1727</v>
       </c>
       <c r="V14" t="n">
         <v>-2.9474</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.7941</v>
+        <v>-4.857900000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.7761</v>
+        <v>-6.840000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.981900000000001</v>
+        <v>1.981999999999998</v>
       </c>
       <c r="G15" t="n">
         <v>-13.2707</v>
@@ -1603,7 +1603,7 @@
         <v>-2.2139</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3938999999999995</v>
+        <v>0.3939000000000004</v>
       </c>
       <c r="M15" t="n">
         <v>-11.4505</v>
@@ -1624,13 +1624,13 @@
         <v>23.7869</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6892</v>
+        <v>2.625</v>
       </c>
       <c r="T15" t="n">
-        <v>3.397500000000001</v>
+        <v>4.3333</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.7083</v>
+        <v>-1.7081</v>
       </c>
       <c r="V15" t="n">
         <v>-6.1059</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.141299999999999</v>
+        <v>7.8918</v>
       </c>
       <c r="E16" t="n">
-        <v>9.447100000000001</v>
+        <v>9.141500000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3058</v>
+        <v>-1.2496</v>
       </c>
       <c r="G16" t="n">
         <v>5.0011</v>
@@ -1702,13 +1702,13 @@
         <v>1.5858</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0581</v>
+        <v>-0.3075</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7453</v>
+        <v>0.4397</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8034</v>
+        <v>-0.7472</v>
       </c>
       <c r="V16" t="n">
         <v>1.8107</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. MAERIEN</t>
+          <t>F. DAYER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2177</v>
+        <v>2.3352</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8994</v>
+        <v>0.0312</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3183</v>
+        <v>2.304</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0254</v>
+        <v>3.4968</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1442</v>
+        <v>1.9931</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1187</v>
+        <v>1.5037</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3731</v>
+        <v>3.2123</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4975</v>
+        <v>1.3525</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1244</v>
+        <v>1.8598</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3985</v>
+        <v>0.2845</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6417</v>
+        <v>0.6407</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2431</v>
+        <v>-0.3562</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>-6.1449</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4588</v>
+        <v>-0.2149</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2636</v>
+        <v>-0.054</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8048</v>
+        <v>-0.1609</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2666</v>
+        <v>3.0178</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.0178</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.451</v>
+        <v>2.0165</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5419</v>
+        <v>2.0055</v>
       </c>
       <c r="G18" t="n">
         <v>0.6713</v>
@@ -1858,13 +1858,13 @@
         <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4362</v>
+        <v>0.1293</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4957</v>
+        <v>0.5976</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.4683</v>
       </c>
       <c r="V18" t="n">
         <v>1.8107</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARTÍNEZ GUZMÁN</t>
+          <t>L. MAERIEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2053</v>
+        <v>1.8124</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2053</v>
+        <v>-0.138</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.9504</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2053</v>
+        <v>1.0254</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.1442</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2053</v>
+        <v>-0.1187</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2053</v>
+        <v>-0.3731</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.4975</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2053</v>
+        <v>0.1244</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.3985</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.6417</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.2431</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.0535</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.1727</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MORALES MUÑOZ</t>
+          <t>J. MARTÍNEZ GUZMÁN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,31 +1969,31 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9053</v>
+        <v>1.2053</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9053</v>
+        <v>1.2053</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9053</v>
+        <v>1.2053</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6027</v>
+        <v>1.2053</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9053</v>
+        <v>1.2053</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6027</v>
+        <v>1.2053</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. DAYER</t>
+          <t>J. MORALES MUÑOZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8353</v>
+        <v>0.9053</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0894</v>
+        <v>0.9053</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9246</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>3.4968</v>
+        <v>0.9053</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9931</v>
+        <v>0.3027</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5037</v>
+        <v>0.6027</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2123</v>
+        <v>0.9053</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3525</v>
+        <v>0.3027</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8598</v>
+        <v>0.6027</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2845</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6407</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3562</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-6.1449</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7148</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1745</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5403</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>3.0178</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.0178</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8158</v>
+        <v>-0.0554</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4305</v>
+        <v>-0.3845</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3852</v>
+        <v>0.3291</v>
       </c>
       <c r="G22" t="n">
         <v>-0.466</v>
@@ -2170,13 +2170,13 @@
         <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7554999999999999</v>
+        <v>-0.1157</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1197</v>
+        <v>0.3047</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3642</v>
+        <v>-0.4204</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2666</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. BAMADU</t>
+          <t>J. MORALES MUNOZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2893</v>
+        <v>-1.6305</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5598</v>
+        <v>-3.6222</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2705</v>
+        <v>1.9917</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1191</v>
+        <v>1.7173</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2441</v>
+        <v>-0.1713</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.125</v>
+        <v>1.8886</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9751</v>
+        <v>1.8517</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5739</v>
+        <v>-0.2687</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5988</v>
+        <v>2.1204</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.856</v>
+        <v>-0.1344</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3298</v>
+        <v>0.0973</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5262</v>
+        <v>-0.2317</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1805</v>
+        <v>-3.1716</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9733</v>
+        <v>-4.9556</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.228</v>
+        <v>-0.1762</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5616</v>
+        <v>-0.5183</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3336</v>
+        <v>0.3421</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3434</v>
+        <v>-1.7322</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0866</v>
+        <v>-2.4753</v>
       </c>
       <c r="F24" t="n">
         <v>0.7431</v>
@@ -2326,10 +2326,10 @@
         <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1307</v>
+        <v>-0.5195</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3634</v>
+        <v>0.2479</v>
       </c>
       <c r="U24" t="n">
         <v>-0.7674</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>M. BAMADU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9936</v>
+        <v>-2.1136</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.504</v>
+        <v>-2.3561</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5104</v>
+        <v>0.2425</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.3045</v>
+        <v>0.1191</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4154</v>
+        <v>1.2441</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1109</v>
+        <v>-1.125</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.1491</v>
+        <v>0.9751</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.2372</v>
+        <v>1.5739</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0881</v>
+        <v>-0.5988</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1554</v>
+        <v>-0.856</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1782</v>
+        <v>-0.3298</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0228</v>
+        <v>-0.5262</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.784</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q25" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3615</v>
+        <v>-0.0523</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3816</v>
+        <v>-0.3578</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7431</v>
+        <v>0.3055</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. MORALES MUNOZ</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.1514</v>
+        <v>-2.8036</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.539</v>
+        <v>-4.3003</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3876</v>
+        <v>1.4967</v>
       </c>
       <c r="G26" t="n">
-        <v>1.7173</v>
+        <v>-1.3045</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1713</v>
+        <v>-1.4154</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8886</v>
+        <v>0.1109</v>
       </c>
       <c r="J26" t="n">
-        <v>1.8517</v>
+        <v>-1.1491</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2687</v>
+        <v>-1.2372</v>
       </c>
       <c r="L26" t="n">
-        <v>2.1204</v>
+        <v>0.0881</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1344</v>
+        <v>-0.1554</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0973</v>
+        <v>-0.1782</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2317</v>
+        <v>0.0228</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.1716</v>
+        <v>-1.784</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.9556</v>
+        <v>-2.9733</v>
       </c>
       <c r="R26" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.6971</v>
+        <v>0.5515</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.4351</v>
+        <v>-0.1779</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.262</v>
+        <v>0.7294</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>5.793999999999999</v>
+        <v>7.831200000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.981999999999998</v>
+        <v>-1.9821</v>
       </c>
       <c r="F27" t="n">
-        <v>7.7758</v>
+        <v>9.8134</v>
       </c>
       <c r="G27" t="n">
         <v>13.2705</v>
@@ -2542,7 +2542,7 @@
         <v>2.4884</v>
       </c>
       <c r="M27" t="n">
-        <v>1.8199</v>
+        <v>1.819900000000001</v>
       </c>
       <c r="N27" t="n">
         <v>2.214</v>
@@ -2560,13 +2560,13 @@
         <v>11.8934</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.6891</v>
+        <v>0.3482000000000001</v>
       </c>
       <c r="T27" t="n">
         <v>1.7081</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.3974</v>
+        <v>-1.3599</v>
       </c>
       <c r="V27" t="n">
         <v>6.106</v>
